--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,6 +1165,239 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131452882</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93104</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mylimaksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487080</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666831</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>9 ex</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131453364</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mylimaksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>487080</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666831</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93104</v>
+        <v>93105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93105</v>
+        <v>93108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93108</v>
+        <v>93109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93109</v>
+        <v>93115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>93116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -1170,7 +1170,7 @@
         <v>131452882</v>
       </c>
       <c r="B6" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44535-2021 artfynd.xlsx
+++ b/artfynd/A 44535-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6954561</v>
+        <v>6954560</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486988.8849460244</v>
+        <v>487096</v>
       </c>
       <c r="R2" t="n">
-        <v>6666865.251994799</v>
+        <v>6666830</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,21 +743,11 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>nedbrunnen tallstubbe i hällmarkstallskog</t>
+          <t>på liten klipphylla med tall i sydvänd klippa i barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6954560</v>
+        <v>131452819</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Digerskyttberget, Dlr</t>
+          <t>Mylimaksberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487095.5381599492</v>
+        <v>487080</v>
       </c>
       <c r="R3" t="n">
-        <v>6666829.507668803</v>
+        <v>6666831</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,22 +842,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,74 +873,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>på liten klipphylla med tall i sydvänd klippa i barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1275318</v>
+        <v>131452931</v>
       </c>
       <c r="B4" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svensksjöån, Dlr</t>
+          <t>Mylimaksberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487054.9971957686</v>
+        <v>487098</v>
       </c>
       <c r="R4" t="n">
-        <v>6666794.282388248</v>
+        <v>6666839</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-08-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-08-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,93 +980,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>mindre sydvänd bergsbrant</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>asphögstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1651138</v>
+        <v>1275318</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svensksjöån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487054.9971957686</v>
+        <v>487055</v>
       </c>
       <c r="R5" t="n">
-        <v>6666794.282388248</v>
+        <v>6666794</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,21 +1064,11 @@
           <t>2009-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-08-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1144,12 +1080,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>klipphylla i mindre sydvänd bergsbrant</t>
+          <t>mindre sydvänd bergsbrant</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,45 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131452882</v>
+        <v>6954561</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mylimaksberget, Dlr</t>
+          <t>Östra Digerskyttberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487080</v>
+        <v>486989</v>
       </c>
       <c r="R6" t="n">
-        <v>6666831</v>
+        <v>6666865</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,27 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,16 +1189,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>nedbrunnen tallstubbe i hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1282,11 +1213,11 @@
         <v>131453364</v>
       </c>
       <c r="B7" t="n">
-        <v>57909</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
